--- a/outputs/tp_couches_minces_hors_ligne/outputs/tp_couches_minces/squelette_excel_couches_minces.xlsx
+++ b/outputs/tp_couches_minces_hors_ligne/outputs/tp_couches_minces/squelette_excel_couches_minces.xlsx
@@ -1196,19 +1196,19 @@
         <x:v>dZnS ↓ / dYF₃ →</x:v>
       </x:c>
       <x:c r="B5" s="41" t="n">
-        <x:v>20</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C5" s="41" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="41" t="n">
-        <x:v>80</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E5" s="41" t="n">
-        <x:v>110</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F5" s="41" t="n">
-        <x:v>140</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
         <x:v>Analyse à rédiger</x:v>
@@ -1228,7 +1228,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="43" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="44"/>
       <x:c r="C6" s="44"/>
@@ -1245,7 +1245,7 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="43" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="44"/>
       <x:c r="C7" s="44"/>
@@ -1262,7 +1262,7 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="43" t="n">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B8" s="44"/>
       <x:c r="C8" s="44"/>
@@ -1279,7 +1279,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="43" t="n">
-        <x:v>110</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B9" s="44"/>
       <x:c r="C9" s="44"/>
@@ -1304,7 +1304,7 @@
       <x:c r="E10" s="44"/>
       <x:c r="F10" s="44"/>
       <x:c r="H10" s="32" t="str">
-        <x:v>Limite liée au pas de 30 nm</x:v>
+        <x:v>Limite liée au pas de 20 nm</x:v>
       </x:c>
       <x:c r="I10" s="22"/>
       <x:c r="J10" s="22"/>

--- a/outputs/tp_couches_minces_hors_ligne/outputs/tp_couches_minces/squelette_excel_couches_minces.xlsx
+++ b/outputs/tp_couches_minces_hors_ligne/outputs/tp_couches_minces/squelette_excel_couches_minces.xlsx
@@ -1196,19 +1196,19 @@
         <x:v>dZnS ↓ / dYF₃ →</x:v>
       </x:c>
       <x:c r="B5" s="41" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="41" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D5" s="41" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C5" s="41" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D5" s="41" t="n">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="E5" s="41" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="n">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="F5" s="41" t="n">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
         <x:v>Analyse à rédiger</x:v>
@@ -1228,7 +1228,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="43" t="n">
-        <x:v>60</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="44"/>
       <x:c r="C6" s="44"/>
@@ -1245,7 +1245,7 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="43" t="n">
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="44"/>
       <x:c r="C7" s="44"/>
@@ -1262,7 +1262,7 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="43" t="n">
-        <x:v>100</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B8" s="44"/>
       <x:c r="C8" s="44"/>
@@ -1279,7 +1279,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="43" t="n">
-        <x:v>120</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B9" s="44"/>
       <x:c r="C9" s="44"/>
@@ -1304,7 +1304,7 @@
       <x:c r="E10" s="44"/>
       <x:c r="F10" s="44"/>
       <x:c r="H10" s="32" t="str">
-        <x:v>Limite liée au pas de 20 nm</x:v>
+        <x:v>Limite liée au pas de 30 nm</x:v>
       </x:c>
       <x:c r="I10" s="22"/>
       <x:c r="J10" s="22"/>
